--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411271&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411270&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411269&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411268&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411267&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411266&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>חן כהן – תל גיבורים</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%9f-%d7%9b%d7%94%d7%9f-%d7%aa%d7%9c-%d7%92%d7%99%d7%91%d7%95%d7%a8%d7%99%d7%9d/</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v>תל גיבורים" של  חן כהן הוא שיר חשוף  כואב ומזכך. זהו מסע בזמן אל מחוזות הילדות וההתבגרות בשכונת תל גיבורים בחולון, שעיקרו הוא מסע פנימי אל נבכי דימוי הגוף, החרדה והחיפוש העיקש אחר קבלה עצמית ו"בית" בתוך הנפש. הטקסט והמוזיקה</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>חן כהן – תל גיבורים</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>סהראת – שמש כחולה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%94%d7%a8%d7%90%d7%aa-%d7%a9%d7%9e%d7%a9-%d7%9b%d7%97%d7%95%d7%9c%d7%94/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>השיר "שמש כחולה" של להקת "סהראת" בביצועה של אורטל חאיק פינקל, הוא יצירה מקורית יוצאת דופן בנוף המוזיקלי המקומי. השיר, שנכתב על ידי מקימת ההרכב אתי נאור והולחן על ידי אדיר לוי, מביא  חשיפה רגשית  המטופלת ברגישות ובעוצמה יוצאת דופן.</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>סהראת – שמש כחולה</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
+        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,45 +436,501 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+        <v>תמר ריילי - מרים לי ברמות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>תמר ריילי - מרים לי ברמות</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תמיר גל - דם זה לא מים</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תמיר גל - דם זה לא מים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שניר עוקשי - הבטחות גדולות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שניר עוקשי - הבטחות גדולות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שירז אברהם - את כל הזמן בוכה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שירז אברהם - את כל הזמן בוכה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>רועי לביא - פשוט יודע</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>רועי לביא - פשוט יודע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הראל מויאל - גיבור מנייר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הראל מויאל - גיבור מנייר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלדד ישעיהו - חי את החיים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלדד ישעיהו - חי את החיים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אינו - מועדון הלבבות השבורים</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אינו - מועדון הלבבות השבורים</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אוהב חממה - אהבת חינם</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אוהב חממה - אהבת חינם</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C14" t="str">
         <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
       </c>
-      <c r="D2" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
+      <c r="D14" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -735,202 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-%d7%95%d7%a1%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%99-%d7%aa%d7%9e%d7%99%d7%a8-%d7%91%d7%a8-6-%d7%9e%d7%9b%d7%aa-%d7%96%d7%a7%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הניסיון לחבר בין מוזיקת הרגאיי הקלילה והקצבית של להקת "התקווה 6" לבין ההומור הנונסנסי והדמות האייקונית של "סבא אורי" (בגילומו של תמיר בר) מתגלה כפספוס. השיר אמנם מנסה להצחיק ולייצר מניפסט משעשע על משבר גיל ה-40 והזקנה, אך הוא נופל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>נס X סטילה – מי כמוני</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%a0%d7%a1-x-%d7%a1%d7%98%d7%99%d7%9c%d7%94-%d7%9e%d7%99-%d7%9b%d7%9e%d7%95%d7%a0%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>"מי כמוני" הוא יריית פתיחה לקראת הפרויקט החדש של הצמד נס וסטילה. השיר מביא את כל מה שהפך אותם לאחד הצמדים המסקרנים והמזוהים ביותר בהיפ־הופ הישראלי של השנים האחרונות: ביטים קופצניים, הומור פרוע, ביטחון עצמי מוגזם במכוון, ושפה שמרגישה כאילו</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>נס X סטילה – מי כמוני</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
+        <v>מיוז Nightshift Superstar</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%95%d7%96-nightshift-superstar/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>"Nightshift Superstar" הוא אחד השירים המפתיעים ביותר של Muse בשנים האחרונות. בעוד שהלהקה מזוהה בדרך כלל עם רוק חללי, פרוגרסיבי ודרמטי, כאן היא פונה לטריטוריה הרבה יותר רקידה: שילוב של French House, דיסקו מודרני, פאנק אלקטרוני ורוק אצטדיונים. השיר הוא</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,202 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
+        <v>מיוז Nightshift Superstar</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
+        <v>נועם אוחיון - אחת בלילה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-%d7%95%d7%a1%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%99-%d7%aa%d7%9e%d7%99%d7%a8-%d7%91%d7%a8-6-%d7%9e%d7%9b%d7%aa-%d7%96%d7%a7%d7%a0%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411314&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הניסיון לחבר בין מוזיקת הרגאיי הקלילה והקצבית של להקת "התקווה 6" לבין ההומור הנונסנסי והדמות האייקונית של "סבא אורי" (בגילומו של תמיר בר) מתגלה כפספוס. השיר אמנם מנסה להצחיק ולייצר מניפסט משעשע על משבר גיל ה-40 והזקנה, אך הוא נופל</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
+        <v>נועם אוחיון - אחת בלילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נס X סטילה – מי כמוני</v>
+        <v>שרית אהרון - לומדת לנשום</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a1-x-%d7%a1%d7%98%d7%99%d7%9c%d7%94-%d7%9e%d7%99-%d7%9b%d7%9e%d7%95%d7%a0%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411313&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-10</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>"מי כמוני" הוא יריית פתיחה לקראת הפרויקט החדש של הצמד נס וסטילה. השיר מביא את כל מה שהפך אותם לאחד הצמדים המסקרנים והמזוהים ביותר בהיפ־הופ הישראלי של השנים האחרונות: ביטים קופצניים, הומור פרוע, ביטחון עצמי מוגזם במכוון, ושפה שמרגישה כאילו</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נס X סטילה – מי כמוני</v>
+        <v>שרית אהרון - לומדת לנשום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מיוז Nightshift Superstar</v>
+        <v>רומי רון - בוחרים בטובים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%95%d7%96-nightshift-superstar/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411312&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-10</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>"Nightshift Superstar" הוא אחד השירים המפתיעים ביותר של Muse בשנים האחרונות. בעוד שהלהקה מזוהה בדרך כלל עם רוק חללי, פרוגרסיבי ודרמטי, כאן היא פונה לטריטוריה הרבה יותר רקידה: שילוב של French House, דיסקו מודרני, פאנק אלקטרוני ורוק אצטדיונים. השיר הוא</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,12 +545,582 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מיוז Nightshift Superstar</v>
+        <v>רומי רון - בוחרים בטובים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ראול - שיר לטל</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411311&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ראול - שיר לטל</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עדן חסון - הלוואי שטוב לך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411310&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עדן חסון - הלוואי שטוב לך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נתי - עד שבאת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411309&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נתי - עד שבאת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מתן אלדר - שוב</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411308&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מתן אלדר - שוב</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יהונתן רייר - לשחרר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411307&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יהונתן רייר - לשחרר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411306&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>התקווה 6 &amp; סבא אורי (תמיר בר) - מכת זקנה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלי בי - הבימה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411305&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלי בי - הבימה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אורן להב - מתעלייך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411304&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אורן להב - מתעלייך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411303&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אופירה שופן &amp; ינון יהל - גברים שלא נדע</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>שר-אל - רק את</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411302&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>שר-אל - רק את</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ראובן המלאך - נשבע לך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411301&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>ראובן המלאך - נשבע לך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>קובי ממן - חוף בגבעתיים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411300&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>קובי ממן - חוף בגבעתיים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>נס &amp; סטילה - מי כמוני</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411299&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>נס &amp; סטילה - מי כמוני</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>משה לוק - יה דודי</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411298&amp;sid=c34b403b9845bda4149476b4a5b1dda4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>משה לוק - יה דודי</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>עדן חסון הלוואי שטוב לך</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99-%d7%a9%d7%98%d7%95%d7%91-%d7%9c%d7%9a/</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>השיר "הלוואי שטוב לך" של עדן חסון הוא דוגמה מובהקת לנוסחת שחסון מאמץ כנוסחה בטוחה  – שילוב מדויק בין פופ ים-תיכוני עדכני, טקסטים על לבבות שבורים , ומלודרמה רגשית בסלסול מלנכולי דשמטרתה לדבר אל הלב של הקהל הרחב. השיר בנוי</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>עדן חסון הלוואי שטוב לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בניה ברבי – לילה טוב</v>
+        <v>תהילה עג'מי - לב סגור</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9c%d7%99%d7%9c%d7%94-%d7%98%d7%95%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411329&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "לילה טוב" ששר בניה ברבי, הוא הצצה כנה, לעיתים מכאיבה, אל תוך הנפש של מי שנמצא במרכז הבמה, אך חש צורך לברוח מהרעש ולהתמודד עם השקט. זהו שיר שמייצג את המציאות של לא מעט אמנים בתעשייה, הנקרעים בין אור</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,544 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בניה ברבי – לילה טוב</v>
+        <v>תהילה עג'מי - לב סגור</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רבי אלמוג אסלן - מחרוזת חסידית 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411328&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רבי אלמוג אסלן - מחרוזת חסידית 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ניסים שומינוב - שתיקות ארוכות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411327&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ניסים שומינוב - שתיקות ארוכות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נטע ברזילי &amp; ניבר זנטי - ברבורה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411326&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נטע ברזילי &amp; ניבר זנטי - ברבורה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מתנאל סבח - קולו נדם</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411325&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מתנאל סבח - קולו נדם</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מתן דינו &amp; שפיטה &amp; נטלי פרץ - אין לך מילה 2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411324&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מתן דינו &amp; שפיטה &amp; נטלי פרץ - אין לך מילה 2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מאריאז' - הללויה תהילים קי''ז</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411323&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מאריאז' - הללויה תהילים קי''ז</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ליאן ניגרין - מחרוזת עושה חיים 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411322&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ליאן ניגרין - מחרוזת עושה חיים 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ליאל שרעבי - אחת למיליון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411321&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ליאל שרעבי - אחת למיליון</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוסף שושן - השדים שלך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411320&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוסף שושן - השדים שלך</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>הודיה ויצמן - איך ממשיכים מכאן</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411319&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>הודיה ויצמן - איך ממשיכים מכאן</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלמוג טויטו &amp; יוני מאמוש - עברנו מלחמות נעבור את זה גם הורדה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411318&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלמוג טויטו &amp; יוני מאמוש - עברנו מלחמות נעבור את זה גם הורדה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אליהו חזן - מחרוזת ישמח חתני 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411317&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אליהו חזן - מחרוזת ישמח חתני 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אחיה טמיר - לוחם</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411316&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אחיה טמיר - לוחם</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אושר ביטון - אושר שלי</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411315&amp;sid=cbf06dee34ddcc7520b3f119755efa6b</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אושר ביטון - אושר שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>